--- a/hira_material_automation/output/monthly/202601_202604__epidural_adhesion_barrier__900129__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202604__epidural_adhesion_barrier__900129__normalized.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-04T22:07:51</t>
+          <t>2026-04-14T22:25:49</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ee459696a4bb93d84b25996f01b9772056eec4dc39a0aad49ed8a826ba2b935a</t>
+          <t>97f356b650e3f6f7dd32a4b6ed56642f967f221d0bfcb51d8975696e326d317e</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202604__epidural_adhesion_barrier__900129__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202604__epidural_adhesion_barrier__900129__normalized.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-14T22:25:49</t>
+          <t>2026-04-24T22:24:32</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>97f356b650e3f6f7dd32a4b6ed56642f967f221d0bfcb51d8975696e326d317e</t>
+          <t>31d85bb97856da61fe652987f92e2c8d8e0058b09c900930175064330e69c02d</t>
         </is>
       </c>
     </row>
